--- a/results/excel_reports/resnet50_vit_b_16_white.xlsx
+++ b/results/excel_reports/resnet50_vit_b_16_white.xlsx
@@ -199,12 +199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$2:$U$2</f>
+              <f>'Data'!$B$2:$V$2</f>
             </numRef>
           </val>
         </ser>
@@ -231,12 +231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$3:$U$3</f>
+              <f>'Data'!$B$3:$V$3</f>
             </numRef>
           </val>
         </ser>
@@ -263,12 +263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$4:$U$4</f>
+              <f>'Data'!$B$4:$V$4</f>
             </numRef>
           </val>
         </ser>
@@ -295,12 +295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$5:$U$5</f>
+              <f>'Data'!$B$5:$V$5</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$6:$U$6</f>
+              <f>'Data'!$B$6:$V$6</f>
             </numRef>
           </val>
         </ser>
@@ -359,12 +359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$7:$U$7</f>
+              <f>'Data'!$B$7:$V$7</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$8:$U$8</f>
+              <f>'Data'!$B$8:$V$8</f>
             </numRef>
           </val>
         </ser>
@@ -423,12 +423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$9:$U$9</f>
+              <f>'Data'!$B$9:$V$9</f>
             </numRef>
           </val>
         </ser>
@@ -455,12 +455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$10:$U$10</f>
+              <f>'Data'!$B$10:$V$10</f>
             </numRef>
           </val>
         </ser>
@@ -487,12 +487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$11:$U$11</f>
+              <f>'Data'!$B$11:$V$11</f>
             </numRef>
           </val>
         </ser>
@@ -519,12 +519,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$12:$U$12</f>
+              <f>'Data'!$B$12:$V$12</f>
             </numRef>
           </val>
         </ser>
@@ -551,12 +551,140 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$13:$U$13</f>
+              <f>'Data'!$B$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$16:$V$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="15"/>
+          <order val="15"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$17:$V$17</f>
             </numRef>
           </val>
         </ser>
@@ -633,7 +761,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -943,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -967,6 +1095,7 @@
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="7" customWidth="1" min="20" max="20"/>
     <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1035,809 +1164,1128 @@
       <c r="U1" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="V1" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c3f</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.926</v>
       </c>
       <c r="D2" t="n">
-        <v>0.926</v>
+        <v>0.909</v>
       </c>
       <c r="E2" t="n">
-        <v>0.925</v>
+        <v>0.894</v>
       </c>
       <c r="F2" t="n">
-        <v>0.914</v>
+        <v>0.888</v>
       </c>
       <c r="G2" t="n">
-        <v>0.913</v>
+        <v>0.874</v>
       </c>
       <c r="H2" t="n">
-        <v>0.891</v>
+        <v>0.853</v>
       </c>
       <c r="I2" t="n">
-        <v>0.885</v>
+        <v>0.833</v>
       </c>
       <c r="J2" t="n">
-        <v>0.857</v>
+        <v>0.805</v>
       </c>
       <c r="K2" t="n">
-        <v>0.802</v>
+        <v>0.776</v>
       </c>
       <c r="L2" t="n">
-        <v>0.699</v>
+        <v>0.737</v>
       </c>
       <c r="M2" t="n">
-        <v>0.644</v>
+        <v>0.676</v>
       </c>
       <c r="N2" t="n">
-        <v>0.605</v>
+        <v>0.627</v>
       </c>
       <c r="O2" t="n">
-        <v>0.585</v>
+        <v>0.546</v>
       </c>
       <c r="P2" t="n">
-        <v>0.529</v>
+        <v>0.473</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.484</v>
+        <v>0.396</v>
       </c>
       <c r="R2" t="n">
-        <v>0.408</v>
+        <v>0.296</v>
       </c>
       <c r="S2" t="n">
-        <v>0.297</v>
+        <v>0.192</v>
       </c>
       <c r="T2" t="n">
-        <v>0.165</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.926</v>
       </c>
       <c r="D3" t="n">
-        <v>0.931</v>
+        <v>0.913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.921</v>
+        <v>0.888</v>
       </c>
       <c r="G3" t="n">
-        <v>0.919</v>
+        <v>0.876</v>
       </c>
       <c r="H3" t="n">
-        <v>0.91</v>
+        <v>0.865</v>
       </c>
       <c r="I3" t="n">
-        <v>0.893</v>
+        <v>0.837</v>
       </c>
       <c r="J3" t="n">
-        <v>0.877</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.864</v>
+        <v>0.767</v>
       </c>
       <c r="L3" t="n">
-        <v>0.848</v>
+        <v>0.731</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.786</v>
+        <v>0.617</v>
       </c>
       <c r="O3" t="n">
-        <v>0.742</v>
+        <v>0.545</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.468</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.625</v>
+        <v>0.39</v>
       </c>
       <c r="R3" t="n">
-        <v>0.542</v>
+        <v>0.307</v>
       </c>
       <c r="S3" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0.255</v>
+        <v>0.104</v>
       </c>
       <c r="U3" t="n">
-        <v>0.066</v>
+        <v>0.03</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.859</v>
+        <v>0.926</v>
       </c>
       <c r="D4" t="n">
-        <v>0.777</v>
+        <v>0.913</v>
       </c>
       <c r="E4" t="n">
-        <v>0.708</v>
+        <v>0.895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.632</v>
+        <v>0.879</v>
       </c>
       <c r="G4" t="n">
-        <v>0.554</v>
+        <v>0.872</v>
       </c>
       <c r="H4" t="n">
-        <v>0.485</v>
+        <v>0.848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.442</v>
+        <v>0.822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.378</v>
+        <v>0.791</v>
       </c>
       <c r="K4" t="n">
-        <v>0.313</v>
+        <v>0.761</v>
       </c>
       <c r="L4" t="n">
-        <v>0.288</v>
+        <v>0.721</v>
       </c>
       <c r="M4" t="n">
-        <v>0.237</v>
+        <v>0.669</v>
       </c>
       <c r="N4" t="n">
-        <v>0.19</v>
+        <v>0.594</v>
       </c>
       <c r="O4" t="n">
-        <v>0.158</v>
+        <v>0.522</v>
       </c>
       <c r="P4" t="n">
-        <v>0.111</v>
+        <v>0.458</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.073</v>
+        <v>0.37</v>
       </c>
       <c r="R4" t="n">
-        <v>0.053</v>
+        <v>0.276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.029</v>
+        <v>0.162</v>
       </c>
       <c r="T4" t="n">
-        <v>0.011</v>
+        <v>0.067</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005</v>
+        <v>0.019</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.875</v>
+        <v>0.926</v>
       </c>
       <c r="D5" t="n">
-        <v>0.83</v>
+        <v>0.913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.789</v>
+        <v>0.895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.757</v>
+        <v>0.879</v>
       </c>
       <c r="G5" t="n">
-        <v>0.708</v>
+        <v>0.872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.848</v>
       </c>
       <c r="I5" t="n">
-        <v>0.634</v>
+        <v>0.822</v>
       </c>
       <c r="J5" t="n">
-        <v>0.596</v>
+        <v>0.791</v>
       </c>
       <c r="K5" t="n">
-        <v>0.555</v>
+        <v>0.761</v>
       </c>
       <c r="L5" t="n">
-        <v>0.503</v>
+        <v>0.721</v>
       </c>
       <c r="M5" t="n">
-        <v>0.46</v>
+        <v>0.669</v>
       </c>
       <c r="N5" t="n">
-        <v>0.388</v>
+        <v>0.594</v>
       </c>
       <c r="O5" t="n">
-        <v>0.325</v>
+        <v>0.522</v>
       </c>
       <c r="P5" t="n">
-        <v>0.281</v>
+        <v>0.458</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.224</v>
+        <v>0.37</v>
       </c>
       <c r="R5" t="n">
-        <v>0.188</v>
+        <v>0.276</v>
       </c>
       <c r="S5" t="n">
-        <v>0.134</v>
+        <v>0.162</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="U5" t="n">
-        <v>0.033</v>
+        <v>0.019</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.909</v>
+        <v>0.898</v>
       </c>
       <c r="D6" t="n">
-        <v>0.892</v>
+        <v>0.864</v>
       </c>
       <c r="E6" t="n">
-        <v>0.87</v>
+        <v>0.823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.843</v>
+        <v>0.788</v>
       </c>
       <c r="G6" t="n">
-        <v>0.82</v>
+        <v>0.738</v>
       </c>
       <c r="H6" t="n">
-        <v>0.792</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.74</v>
+        <v>0.655</v>
       </c>
       <c r="J6" t="n">
-        <v>0.704</v>
+        <v>0.621</v>
       </c>
       <c r="K6" t="n">
-        <v>0.67</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.639</v>
+        <v>0.508</v>
       </c>
       <c r="M6" t="n">
-        <v>0.597</v>
+        <v>0.448</v>
       </c>
       <c r="N6" t="n">
-        <v>0.538</v>
+        <v>0.381</v>
       </c>
       <c r="O6" t="n">
-        <v>0.483</v>
+        <v>0.331</v>
       </c>
       <c r="P6" t="n">
-        <v>0.42</v>
+        <v>0.273</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.337</v>
+        <v>0.233</v>
       </c>
       <c r="R6" t="n">
-        <v>0.253</v>
+        <v>0.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0.178</v>
+        <v>0.121</v>
       </c>
       <c r="T6" t="n">
-        <v>0.105</v>
+        <v>0.054</v>
       </c>
       <c r="U6" t="n">
-        <v>0.041</v>
+        <v>0.017</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.848</v>
+        <v>0.924</v>
       </c>
       <c r="D7" t="n">
-        <v>0.771</v>
+        <v>0.911</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.603</v>
+        <v>0.868</v>
       </c>
       <c r="G7" t="n">
-        <v>0.541</v>
+        <v>0.852</v>
       </c>
       <c r="H7" t="n">
-        <v>0.471</v>
+        <v>0.833</v>
       </c>
       <c r="I7" t="n">
-        <v>0.412</v>
+        <v>0.801</v>
       </c>
       <c r="J7" t="n">
-        <v>0.364</v>
+        <v>0.761</v>
       </c>
       <c r="K7" t="n">
-        <v>0.309</v>
+        <v>0.726</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.641</v>
       </c>
       <c r="N7" t="n">
-        <v>0.154</v>
+        <v>0.573</v>
       </c>
       <c r="O7" t="n">
-        <v>0.103</v>
+        <v>0.498</v>
       </c>
       <c r="P7" t="n">
-        <v>0.082</v>
+        <v>0.446</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.049</v>
+        <v>0.357</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03</v>
+        <v>0.272</v>
       </c>
       <c r="S7" t="n">
-        <v>0.024</v>
+        <v>0.195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.006</v>
+        <v>0.097</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004</v>
+        <v>0.036</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.863</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.788</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.712</v>
+        <v>0.928</v>
       </c>
       <c r="F8" t="n">
-        <v>0.622</v>
+        <v>0.922</v>
       </c>
       <c r="G8" t="n">
-        <v>0.552</v>
+        <v>0.92</v>
       </c>
       <c r="H8" t="n">
-        <v>0.502</v>
+        <v>0.91</v>
       </c>
       <c r="I8" t="n">
-        <v>0.439</v>
+        <v>0.893</v>
       </c>
       <c r="J8" t="n">
-        <v>0.401</v>
+        <v>0.877</v>
       </c>
       <c r="K8" t="n">
-        <v>0.344</v>
+        <v>0.864</v>
       </c>
       <c r="L8" t="n">
-        <v>0.297</v>
+        <v>0.848</v>
       </c>
       <c r="M8" t="n">
-        <v>0.244</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.197</v>
+        <v>0.786</v>
       </c>
       <c r="O8" t="n">
-        <v>0.156</v>
+        <v>0.742</v>
       </c>
       <c r="P8" t="n">
-        <v>0.109</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.078</v>
+        <v>0.625</v>
       </c>
       <c r="R8" t="n">
-        <v>0.057</v>
+        <v>0.542</v>
       </c>
       <c r="S8" t="n">
-        <v>0.026</v>
+        <v>0.428</v>
       </c>
       <c r="T8" t="n">
-        <v>0.014</v>
+        <v>0.254</v>
       </c>
       <c r="U8" t="n">
-        <v>0.005</v>
+        <v>0.066</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.919</v>
+        <v>0.857</v>
       </c>
       <c r="D9" t="n">
-        <v>0.906</v>
+        <v>0.783</v>
       </c>
       <c r="E9" t="n">
-        <v>0.893</v>
+        <v>0.704</v>
       </c>
       <c r="F9" t="n">
-        <v>0.884</v>
+        <v>0.624</v>
       </c>
       <c r="G9" t="n">
-        <v>0.873</v>
+        <v>0.569</v>
       </c>
       <c r="H9" t="n">
-        <v>0.848</v>
+        <v>0.506</v>
       </c>
       <c r="I9" t="n">
-        <v>0.837</v>
+        <v>0.452</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.389</v>
       </c>
       <c r="K9" t="n">
-        <v>0.783</v>
+        <v>0.336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.757</v>
+        <v>0.285</v>
       </c>
       <c r="M9" t="n">
-        <v>0.708</v>
+        <v>0.246</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653</v>
+        <v>0.191</v>
       </c>
       <c r="O9" t="n">
-        <v>0.604</v>
+        <v>0.153</v>
       </c>
       <c r="P9" t="n">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.43</v>
+        <v>0.077</v>
       </c>
       <c r="R9" t="n">
-        <v>0.321</v>
+        <v>0.053</v>
       </c>
       <c r="S9" t="n">
-        <v>0.218</v>
+        <v>0.028</v>
       </c>
       <c r="T9" t="n">
-        <v>0.107</v>
+        <v>0.012</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.749</v>
+        <v>0.875</v>
       </c>
       <c r="D10" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="E10" t="n">
-        <v>0.503</v>
+        <v>0.789</v>
       </c>
       <c r="F10" t="n">
-        <v>0.401</v>
+        <v>0.756</v>
       </c>
       <c r="G10" t="n">
-        <v>0.316</v>
+        <v>0.708</v>
       </c>
       <c r="H10" t="n">
-        <v>0.234</v>
+        <v>0.681</v>
       </c>
       <c r="I10" t="n">
-        <v>0.181</v>
+        <v>0.634</v>
       </c>
       <c r="J10" t="n">
-        <v>0.141</v>
+        <v>0.595</v>
       </c>
       <c r="K10" t="n">
-        <v>0.096</v>
+        <v>0.555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.077</v>
+        <v>0.504</v>
       </c>
       <c r="M10" t="n">
-        <v>0.052</v>
+        <v>0.46</v>
       </c>
       <c r="N10" t="n">
-        <v>0.036</v>
+        <v>0.388</v>
       </c>
       <c r="O10" t="n">
-        <v>0.023</v>
+        <v>0.325</v>
       </c>
       <c r="P10" t="n">
-        <v>0.021</v>
+        <v>0.281</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.015</v>
+        <v>0.224</v>
       </c>
       <c r="R10" t="n">
-        <v>0.011</v>
+        <v>0.189</v>
       </c>
       <c r="S10" t="n">
-        <v>0.007</v>
+        <v>0.134</v>
       </c>
       <c r="T10" t="n">
-        <v>0.004</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002</v>
+        <v>0.033</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.852</v>
+        <v>0.908</v>
       </c>
       <c r="D11" t="n">
-        <v>0.742</v>
+        <v>0.89</v>
       </c>
       <c r="E11" t="n">
-        <v>0.653</v>
+        <v>0.868</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.843</v>
       </c>
       <c r="G11" t="n">
-        <v>0.495</v>
+        <v>0.82</v>
       </c>
       <c r="H11" t="n">
-        <v>0.413</v>
+        <v>0.792</v>
       </c>
       <c r="I11" t="n">
-        <v>0.351</v>
+        <v>0.741</v>
       </c>
       <c r="J11" t="n">
-        <v>0.29</v>
+        <v>0.704</v>
       </c>
       <c r="K11" t="n">
-        <v>0.235</v>
+        <v>0.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.164</v>
+        <v>0.639</v>
       </c>
       <c r="M11" t="n">
-        <v>0.123</v>
+        <v>0.597</v>
       </c>
       <c r="N11" t="n">
-        <v>0.092</v>
+        <v>0.539</v>
       </c>
       <c r="O11" t="n">
-        <v>0.068</v>
+        <v>0.483</v>
       </c>
       <c r="P11" t="n">
-        <v>0.044</v>
+        <v>0.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.024</v>
+        <v>0.337</v>
       </c>
       <c r="R11" t="n">
-        <v>0.015</v>
+        <v>0.253</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01</v>
+        <v>0.178</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003</v>
+        <v>0.105</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005</v>
+        <v>0.041</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>smoothgrad</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.919</v>
+        <v>0.848</v>
       </c>
       <c r="D12" t="n">
-        <v>0.897</v>
+        <v>0.771</v>
       </c>
       <c r="E12" t="n">
-        <v>0.857</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.603</v>
       </c>
       <c r="G12" t="n">
-        <v>0.773</v>
+        <v>0.541</v>
       </c>
       <c r="H12" t="n">
-        <v>0.725</v>
+        <v>0.471</v>
       </c>
       <c r="I12" t="n">
-        <v>0.668</v>
+        <v>0.412</v>
       </c>
       <c r="J12" t="n">
-        <v>0.606</v>
+        <v>0.364</v>
       </c>
       <c r="K12" t="n">
-        <v>0.551</v>
+        <v>0.309</v>
       </c>
       <c r="L12" t="n">
-        <v>0.482</v>
+        <v>0.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0.425</v>
+        <v>0.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.354</v>
+        <v>0.154</v>
       </c>
       <c r="O12" t="n">
-        <v>0.289</v>
+        <v>0.103</v>
       </c>
       <c r="P12" t="n">
-        <v>0.237</v>
+        <v>0.082</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.158</v>
+        <v>0.049</v>
       </c>
       <c r="R12" t="n">
-        <v>0.102</v>
+        <v>0.03</v>
       </c>
       <c r="S12" t="n">
-        <v>0.058</v>
+        <v>0.024</v>
       </c>
       <c r="T12" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="U12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>integrated_gradients</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>occlusion</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B17" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C17" t="n">
         <v>0.914</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D17" t="n">
         <v>0.904</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E17" t="n">
         <v>0.883</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F17" t="n">
         <v>0.85</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G17" t="n">
         <v>0.82</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H17" t="n">
         <v>0.778</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I17" t="n">
         <v>0.734</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J17" t="n">
         <v>0.674</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K17" t="n">
         <v>0.605</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L17" t="n">
         <v>0.547</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M17" t="n">
         <v>0.483</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N17" t="n">
         <v>0.413</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O17" t="n">
         <v>0.335</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P17" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q17" t="n">
         <v>0.185</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R17" t="n">
         <v>0.126</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S17" t="n">
         <v>0.077</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T17" t="n">
         <v>0.029</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U17" t="n">
         <v>0.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.001</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel_reports/resnet50_vit_b_16_white.xlsx
+++ b/results/excel_reports/resnet50_vit_b_16_white.xlsx
@@ -592,102 +592,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="13"/>
-          <order val="13"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$15:$V$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="14"/>
-          <order val="14"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$16:$V$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="15"/>
-          <order val="15"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$17:$V$17</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -761,7 +665,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1071,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1171,68 +1075,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.926</v>
+        <v>0.733</v>
       </c>
       <c r="D2" t="n">
-        <v>0.909</v>
+        <v>0.612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.894</v>
+        <v>0.499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.888</v>
+        <v>0.416</v>
       </c>
       <c r="G2" t="n">
-        <v>0.874</v>
+        <v>0.317</v>
       </c>
       <c r="H2" t="n">
-        <v>0.853</v>
+        <v>0.254</v>
       </c>
       <c r="I2" t="n">
-        <v>0.833</v>
+        <v>0.189</v>
       </c>
       <c r="J2" t="n">
-        <v>0.805</v>
+        <v>0.136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.776</v>
+        <v>0.104</v>
       </c>
       <c r="L2" t="n">
-        <v>0.737</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.676</v>
+        <v>0.051</v>
       </c>
       <c r="N2" t="n">
-        <v>0.627</v>
+        <v>0.035</v>
       </c>
       <c r="O2" t="n">
-        <v>0.546</v>
+        <v>0.027</v>
       </c>
       <c r="P2" t="n">
-        <v>0.473</v>
+        <v>0.024</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.396</v>
+        <v>0.019</v>
       </c>
       <c r="R2" t="n">
-        <v>0.296</v>
+        <v>0.013</v>
       </c>
       <c r="S2" t="n">
-        <v>0.192</v>
+        <v>0.006</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="V2" t="n">
         <v>0.001</v>
@@ -1241,68 +1145,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.926</v>
+        <v>0.848</v>
       </c>
       <c r="D3" t="n">
-        <v>0.913</v>
+        <v>0.74</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>0.651</v>
       </c>
       <c r="F3" t="n">
-        <v>0.888</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.876</v>
+        <v>0.495</v>
       </c>
       <c r="H3" t="n">
-        <v>0.865</v>
+        <v>0.409</v>
       </c>
       <c r="I3" t="n">
-        <v>0.837</v>
+        <v>0.357</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.767</v>
+        <v>0.235</v>
       </c>
       <c r="L3" t="n">
-        <v>0.731</v>
+        <v>0.167</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="N3" t="n">
-        <v>0.617</v>
+        <v>0.092</v>
       </c>
       <c r="O3" t="n">
-        <v>0.545</v>
+        <v>0.068</v>
       </c>
       <c r="P3" t="n">
-        <v>0.468</v>
+        <v>0.047</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.39</v>
+        <v>0.025</v>
       </c>
       <c r="R3" t="n">
-        <v>0.307</v>
+        <v>0.015</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="T3" t="n">
-        <v>0.104</v>
+        <v>0.003</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03</v>
+        <v>0.005</v>
       </c>
       <c r="V3" t="n">
         <v>0.001</v>
@@ -1311,68 +1215,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.926</v>
+        <v>0.848</v>
       </c>
       <c r="D4" t="n">
-        <v>0.913</v>
+        <v>0.771</v>
       </c>
       <c r="E4" t="n">
-        <v>0.895</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.879</v>
+        <v>0.603</v>
       </c>
       <c r="G4" t="n">
-        <v>0.872</v>
+        <v>0.541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.848</v>
+        <v>0.471</v>
       </c>
       <c r="I4" t="n">
-        <v>0.822</v>
+        <v>0.412</v>
       </c>
       <c r="J4" t="n">
-        <v>0.791</v>
+        <v>0.364</v>
       </c>
       <c r="K4" t="n">
-        <v>0.761</v>
+        <v>0.309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.721</v>
+        <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0.669</v>
+        <v>0.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.594</v>
+        <v>0.154</v>
       </c>
       <c r="O4" t="n">
-        <v>0.522</v>
+        <v>0.103</v>
       </c>
       <c r="P4" t="n">
-        <v>0.458</v>
+        <v>0.082</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.37</v>
+        <v>0.049</v>
       </c>
       <c r="R4" t="n">
-        <v>0.276</v>
+        <v>0.03</v>
       </c>
       <c r="S4" t="n">
-        <v>0.162</v>
+        <v>0.024</v>
       </c>
       <c r="T4" t="n">
-        <v>0.067</v>
+        <v>0.006</v>
       </c>
       <c r="U4" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="V4" t="n">
         <v>0.001</v>
@@ -1381,68 +1285,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.926</v>
+        <v>0.857</v>
       </c>
       <c r="D5" t="n">
-        <v>0.913</v>
+        <v>0.783</v>
       </c>
       <c r="E5" t="n">
-        <v>0.895</v>
+        <v>0.704</v>
       </c>
       <c r="F5" t="n">
-        <v>0.879</v>
+        <v>0.624</v>
       </c>
       <c r="G5" t="n">
-        <v>0.872</v>
+        <v>0.569</v>
       </c>
       <c r="H5" t="n">
-        <v>0.848</v>
+        <v>0.506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.822</v>
+        <v>0.452</v>
       </c>
       <c r="J5" t="n">
-        <v>0.791</v>
+        <v>0.389</v>
       </c>
       <c r="K5" t="n">
-        <v>0.761</v>
+        <v>0.336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.721</v>
+        <v>0.285</v>
       </c>
       <c r="M5" t="n">
-        <v>0.669</v>
+        <v>0.246</v>
       </c>
       <c r="N5" t="n">
-        <v>0.594</v>
+        <v>0.191</v>
       </c>
       <c r="O5" t="n">
-        <v>0.522</v>
+        <v>0.153</v>
       </c>
       <c r="P5" t="n">
-        <v>0.458</v>
+        <v>0.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.37</v>
+        <v>0.077</v>
       </c>
       <c r="R5" t="n">
-        <v>0.276</v>
+        <v>0.053</v>
       </c>
       <c r="S5" t="n">
-        <v>0.162</v>
+        <v>0.028</v>
       </c>
       <c r="T5" t="n">
-        <v>0.067</v>
+        <v>0.012</v>
       </c>
       <c r="U5" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="V5" t="n">
         <v>0.001</v>
@@ -1451,68 +1355,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.898</v>
+        <v>0.863</v>
       </c>
       <c r="D6" t="n">
-        <v>0.864</v>
+        <v>0.788</v>
       </c>
       <c r="E6" t="n">
-        <v>0.823</v>
+        <v>0.712</v>
       </c>
       <c r="F6" t="n">
-        <v>0.788</v>
+        <v>0.622</v>
       </c>
       <c r="G6" t="n">
-        <v>0.738</v>
+        <v>0.552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.502</v>
       </c>
       <c r="I6" t="n">
-        <v>0.655</v>
+        <v>0.439</v>
       </c>
       <c r="J6" t="n">
-        <v>0.621</v>
+        <v>0.401</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.508</v>
+        <v>0.297</v>
       </c>
       <c r="M6" t="n">
-        <v>0.448</v>
+        <v>0.244</v>
       </c>
       <c r="N6" t="n">
-        <v>0.381</v>
+        <v>0.197</v>
       </c>
       <c r="O6" t="n">
-        <v>0.331</v>
+        <v>0.156</v>
       </c>
       <c r="P6" t="n">
-        <v>0.273</v>
+        <v>0.109</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.233</v>
+        <v>0.078</v>
       </c>
       <c r="R6" t="n">
-        <v>0.18</v>
+        <v>0.057</v>
       </c>
       <c r="S6" t="n">
-        <v>0.121</v>
+        <v>0.026</v>
       </c>
       <c r="T6" t="n">
-        <v>0.054</v>
+        <v>0.014</v>
       </c>
       <c r="U6" t="n">
-        <v>0.017</v>
+        <v>0.005</v>
       </c>
       <c r="V6" t="n">
         <v>0.001</v>
@@ -1521,68 +1425,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.924</v>
+        <v>0.914</v>
       </c>
       <c r="D7" t="n">
-        <v>0.911</v>
+        <v>0.904</v>
       </c>
       <c r="E7" t="n">
-        <v>0.889</v>
+        <v>0.883</v>
       </c>
       <c r="F7" t="n">
-        <v>0.868</v>
+        <v>0.85</v>
       </c>
       <c r="G7" t="n">
-        <v>0.852</v>
+        <v>0.82</v>
       </c>
       <c r="H7" t="n">
-        <v>0.833</v>
+        <v>0.778</v>
       </c>
       <c r="I7" t="n">
-        <v>0.801</v>
+        <v>0.734</v>
       </c>
       <c r="J7" t="n">
-        <v>0.761</v>
+        <v>0.674</v>
       </c>
       <c r="K7" t="n">
-        <v>0.726</v>
+        <v>0.605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="M7" t="n">
-        <v>0.641</v>
+        <v>0.483</v>
       </c>
       <c r="N7" t="n">
-        <v>0.573</v>
+        <v>0.413</v>
       </c>
       <c r="O7" t="n">
-        <v>0.498</v>
+        <v>0.335</v>
       </c>
       <c r="P7" t="n">
-        <v>0.446</v>
+        <v>0.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.357</v>
+        <v>0.185</v>
       </c>
       <c r="R7" t="n">
-        <v>0.272</v>
+        <v>0.126</v>
       </c>
       <c r="S7" t="n">
-        <v>0.195</v>
+        <v>0.077</v>
       </c>
       <c r="T7" t="n">
-        <v>0.097</v>
+        <v>0.029</v>
       </c>
       <c r="U7" t="n">
-        <v>0.036</v>
+        <v>0.01</v>
       </c>
       <c r="V7" t="n">
         <v>0.001</v>
@@ -1591,68 +1495,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="E8" t="n">
-        <v>0.928</v>
+        <v>0.789</v>
       </c>
       <c r="F8" t="n">
-        <v>0.922</v>
+        <v>0.756</v>
       </c>
       <c r="G8" t="n">
-        <v>0.92</v>
+        <v>0.708</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.681</v>
       </c>
       <c r="I8" t="n">
-        <v>0.893</v>
+        <v>0.634</v>
       </c>
       <c r="J8" t="n">
-        <v>0.877</v>
+        <v>0.595</v>
       </c>
       <c r="K8" t="n">
-        <v>0.864</v>
+        <v>0.555</v>
       </c>
       <c r="L8" t="n">
-        <v>0.848</v>
+        <v>0.504</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="N8" t="n">
-        <v>0.786</v>
+        <v>0.388</v>
       </c>
       <c r="O8" t="n">
-        <v>0.742</v>
+        <v>0.325</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.281</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.625</v>
+        <v>0.224</v>
       </c>
       <c r="R8" t="n">
-        <v>0.542</v>
+        <v>0.189</v>
       </c>
       <c r="S8" t="n">
-        <v>0.428</v>
+        <v>0.134</v>
       </c>
       <c r="T8" t="n">
-        <v>0.254</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.066</v>
+        <v>0.033</v>
       </c>
       <c r="V8" t="n">
         <v>0.001</v>
@@ -1661,68 +1565,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.857</v>
+        <v>0.908</v>
       </c>
       <c r="D9" t="n">
-        <v>0.783</v>
+        <v>0.89</v>
       </c>
       <c r="E9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.704</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.389</v>
-      </c>
       <c r="K9" t="n">
-        <v>0.336</v>
+        <v>0.67</v>
       </c>
       <c r="L9" t="n">
-        <v>0.285</v>
+        <v>0.639</v>
       </c>
       <c r="M9" t="n">
-        <v>0.246</v>
+        <v>0.597</v>
       </c>
       <c r="N9" t="n">
-        <v>0.191</v>
+        <v>0.539</v>
       </c>
       <c r="O9" t="n">
-        <v>0.153</v>
+        <v>0.483</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.077</v>
+        <v>0.337</v>
       </c>
       <c r="R9" t="n">
-        <v>0.053</v>
+        <v>0.253</v>
       </c>
       <c r="S9" t="n">
-        <v>0.028</v>
+        <v>0.178</v>
       </c>
       <c r="T9" t="n">
-        <v>0.012</v>
+        <v>0.105</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005</v>
+        <v>0.041</v>
       </c>
       <c r="V9" t="n">
         <v>0.001</v>
@@ -1731,68 +1635,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.875</v>
+        <v>0.924</v>
       </c>
       <c r="D10" t="n">
-        <v>0.83</v>
+        <v>0.911</v>
       </c>
       <c r="E10" t="n">
-        <v>0.789</v>
+        <v>0.889</v>
       </c>
       <c r="F10" t="n">
-        <v>0.756</v>
+        <v>0.868</v>
       </c>
       <c r="G10" t="n">
-        <v>0.708</v>
+        <v>0.852</v>
       </c>
       <c r="H10" t="n">
-        <v>0.681</v>
+        <v>0.833</v>
       </c>
       <c r="I10" t="n">
-        <v>0.634</v>
+        <v>0.801</v>
       </c>
       <c r="J10" t="n">
-        <v>0.595</v>
+        <v>0.761</v>
       </c>
       <c r="K10" t="n">
-        <v>0.555</v>
+        <v>0.726</v>
       </c>
       <c r="L10" t="n">
-        <v>0.504</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.46</v>
+        <v>0.641</v>
       </c>
       <c r="N10" t="n">
-        <v>0.388</v>
+        <v>0.573</v>
       </c>
       <c r="O10" t="n">
-        <v>0.325</v>
+        <v>0.498</v>
       </c>
       <c r="P10" t="n">
-        <v>0.281</v>
+        <v>0.446</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.224</v>
+        <v>0.357</v>
       </c>
       <c r="R10" t="n">
-        <v>0.189</v>
+        <v>0.272</v>
       </c>
       <c r="S10" t="n">
-        <v>0.134</v>
+        <v>0.195</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="U10" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="V10" t="n">
         <v>0.001</v>
@@ -1801,68 +1705,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.908</v>
+        <v>0.926</v>
       </c>
       <c r="D11" t="n">
-        <v>0.89</v>
+        <v>0.913</v>
       </c>
       <c r="E11" t="n">
-        <v>0.868</v>
+        <v>0.895</v>
       </c>
       <c r="F11" t="n">
-        <v>0.843</v>
+        <v>0.879</v>
       </c>
       <c r="G11" t="n">
-        <v>0.82</v>
+        <v>0.872</v>
       </c>
       <c r="H11" t="n">
-        <v>0.792</v>
+        <v>0.848</v>
       </c>
       <c r="I11" t="n">
-        <v>0.741</v>
+        <v>0.822</v>
       </c>
       <c r="J11" t="n">
-        <v>0.704</v>
+        <v>0.791</v>
       </c>
       <c r="K11" t="n">
-        <v>0.67</v>
+        <v>0.761</v>
       </c>
       <c r="L11" t="n">
-        <v>0.639</v>
+        <v>0.721</v>
       </c>
       <c r="M11" t="n">
-        <v>0.597</v>
+        <v>0.669</v>
       </c>
       <c r="N11" t="n">
-        <v>0.539</v>
+        <v>0.594</v>
       </c>
       <c r="O11" t="n">
-        <v>0.483</v>
+        <v>0.522</v>
       </c>
       <c r="P11" t="n">
-        <v>0.42</v>
+        <v>0.458</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.337</v>
+        <v>0.37</v>
       </c>
       <c r="R11" t="n">
-        <v>0.253</v>
+        <v>0.276</v>
       </c>
       <c r="S11" t="n">
-        <v>0.178</v>
+        <v>0.162</v>
       </c>
       <c r="T11" t="n">
-        <v>0.105</v>
+        <v>0.067</v>
       </c>
       <c r="U11" t="n">
-        <v>0.041</v>
+        <v>0.019</v>
       </c>
       <c r="V11" t="n">
         <v>0.001</v>
@@ -1871,68 +1775,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.848</v>
+        <v>0.926</v>
       </c>
       <c r="D12" t="n">
-        <v>0.771</v>
+        <v>0.909</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.894</v>
       </c>
       <c r="F12" t="n">
-        <v>0.603</v>
+        <v>0.888</v>
       </c>
       <c r="G12" t="n">
-        <v>0.541</v>
+        <v>0.874</v>
       </c>
       <c r="H12" t="n">
-        <v>0.471</v>
+        <v>0.853</v>
       </c>
       <c r="I12" t="n">
-        <v>0.412</v>
+        <v>0.833</v>
       </c>
       <c r="J12" t="n">
-        <v>0.364</v>
+        <v>0.805</v>
       </c>
       <c r="K12" t="n">
-        <v>0.309</v>
+        <v>0.776</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25</v>
+        <v>0.737</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>0.676</v>
       </c>
       <c r="N12" t="n">
-        <v>0.154</v>
+        <v>0.627</v>
       </c>
       <c r="O12" t="n">
-        <v>0.103</v>
+        <v>0.546</v>
       </c>
       <c r="P12" t="n">
-        <v>0.082</v>
+        <v>0.473</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.049</v>
+        <v>0.396</v>
       </c>
       <c r="R12" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="U12" t="n">
         <v>0.03</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.004</v>
       </c>
       <c r="V12" t="n">
         <v>0.001</v>
@@ -1941,68 +1845,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.863</v>
+        <v>0.921</v>
       </c>
       <c r="D13" t="n">
-        <v>0.788</v>
+        <v>0.903</v>
       </c>
       <c r="E13" t="n">
-        <v>0.712</v>
+        <v>0.894</v>
       </c>
       <c r="F13" t="n">
-        <v>0.622</v>
+        <v>0.881</v>
       </c>
       <c r="G13" t="n">
-        <v>0.552</v>
+        <v>0.869</v>
       </c>
       <c r="H13" t="n">
-        <v>0.502</v>
+        <v>0.847</v>
       </c>
       <c r="I13" t="n">
-        <v>0.439</v>
+        <v>0.838</v>
       </c>
       <c r="J13" t="n">
-        <v>0.401</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.344</v>
+        <v>0.779</v>
       </c>
       <c r="L13" t="n">
-        <v>0.297</v>
+        <v>0.755</v>
       </c>
       <c r="M13" t="n">
-        <v>0.244</v>
+        <v>0.713</v>
       </c>
       <c r="N13" t="n">
-        <v>0.197</v>
+        <v>0.651</v>
       </c>
       <c r="O13" t="n">
-        <v>0.156</v>
+        <v>0.604</v>
       </c>
       <c r="P13" t="n">
-        <v>0.109</v>
+        <v>0.532</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.078</v>
+        <v>0.433</v>
       </c>
       <c r="R13" t="n">
-        <v>0.057</v>
+        <v>0.317</v>
       </c>
       <c r="S13" t="n">
-        <v>0.026</v>
+        <v>0.223</v>
       </c>
       <c r="T13" t="n">
-        <v>0.014</v>
+        <v>0.107</v>
       </c>
       <c r="U13" t="n">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="V13" t="n">
         <v>0.001</v>
@@ -2011,284 +1915,86 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.921</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.903</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.894</v>
+        <v>0.928</v>
       </c>
       <c r="F14" t="n">
-        <v>0.881</v>
+        <v>0.922</v>
       </c>
       <c r="G14" t="n">
-        <v>0.869</v>
+        <v>0.92</v>
       </c>
       <c r="H14" t="n">
-        <v>0.847</v>
+        <v>0.91</v>
       </c>
       <c r="I14" t="n">
-        <v>0.838</v>
+        <v>0.893</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.877</v>
       </c>
       <c r="K14" t="n">
-        <v>0.779</v>
+        <v>0.864</v>
       </c>
       <c r="L14" t="n">
-        <v>0.755</v>
+        <v>0.848</v>
       </c>
       <c r="M14" t="n">
-        <v>0.713</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.651</v>
+        <v>0.786</v>
       </c>
       <c r="O14" t="n">
-        <v>0.604</v>
+        <v>0.742</v>
       </c>
       <c r="P14" t="n">
-        <v>0.532</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.433</v>
+        <v>0.625</v>
       </c>
       <c r="R14" t="n">
-        <v>0.317</v>
+        <v>0.542</v>
       </c>
       <c r="S14" t="n">
-        <v>0.223</v>
+        <v>0.428</v>
       </c>
       <c r="T14" t="n">
-        <v>0.107</v>
+        <v>0.254</v>
       </c>
       <c r="U14" t="n">
-        <v>0.022</v>
+        <v>0.066</v>
       </c>
       <c r="V14" t="n">
         <v>0.001</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>random_baseline</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>saliency</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.734</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:V14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/results/excel_reports/resnet50_vit_b_16_white.xlsx
+++ b/results/excel_reports/resnet50_vit_b_16_white.xlsx
@@ -496,102 +496,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$12:$V$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="11"/>
-          <order val="11"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$13:$V$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="12"/>
-          <order val="12"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$14:$V$14</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -665,7 +569,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -975,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1075,68 +979,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.733</v>
+        <v>0.848</v>
       </c>
       <c r="D2" t="n">
-        <v>0.612</v>
+        <v>0.771</v>
       </c>
       <c r="E2" t="n">
-        <v>0.499</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.416</v>
+        <v>0.603</v>
       </c>
       <c r="G2" t="n">
-        <v>0.317</v>
+        <v>0.541</v>
       </c>
       <c r="H2" t="n">
-        <v>0.254</v>
+        <v>0.471</v>
       </c>
       <c r="I2" t="n">
-        <v>0.189</v>
+        <v>0.412</v>
       </c>
       <c r="J2" t="n">
-        <v>0.136</v>
+        <v>0.364</v>
       </c>
       <c r="K2" t="n">
-        <v>0.104</v>
+        <v>0.309</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.051</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.035</v>
+        <v>0.154</v>
       </c>
       <c r="O2" t="n">
-        <v>0.027</v>
+        <v>0.103</v>
       </c>
       <c r="P2" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.024</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>0.006</v>
       </c>
-      <c r="T2" t="n">
-        <v>0.003</v>
-      </c>
       <c r="U2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="V2" t="n">
         <v>0.001</v>
@@ -1145,65 +1049,65 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.848</v>
+        <v>0.857</v>
       </c>
       <c r="D3" t="n">
-        <v>0.74</v>
+        <v>0.783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.651</v>
+        <v>0.704</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.624</v>
       </c>
       <c r="G3" t="n">
-        <v>0.495</v>
+        <v>0.569</v>
       </c>
       <c r="H3" t="n">
-        <v>0.409</v>
+        <v>0.506</v>
       </c>
       <c r="I3" t="n">
-        <v>0.357</v>
+        <v>0.452</v>
       </c>
       <c r="J3" t="n">
-        <v>0.293</v>
+        <v>0.389</v>
       </c>
       <c r="K3" t="n">
-        <v>0.235</v>
+        <v>0.336</v>
       </c>
       <c r="L3" t="n">
-        <v>0.167</v>
+        <v>0.285</v>
       </c>
       <c r="M3" t="n">
-        <v>0.128</v>
+        <v>0.246</v>
       </c>
       <c r="N3" t="n">
-        <v>0.092</v>
+        <v>0.191</v>
       </c>
       <c r="O3" t="n">
-        <v>0.068</v>
+        <v>0.153</v>
       </c>
       <c r="P3" t="n">
-        <v>0.047</v>
+        <v>0.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.025</v>
+        <v>0.077</v>
       </c>
       <c r="R3" t="n">
-        <v>0.015</v>
+        <v>0.053</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01</v>
+        <v>0.028</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="U3" t="n">
         <v>0.005</v>
@@ -1215,68 +1119,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.848</v>
+        <v>0.863</v>
       </c>
       <c r="D4" t="n">
-        <v>0.771</v>
+        <v>0.788</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.603</v>
+        <v>0.622</v>
       </c>
       <c r="G4" t="n">
-        <v>0.541</v>
+        <v>0.552</v>
       </c>
       <c r="H4" t="n">
-        <v>0.471</v>
+        <v>0.502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.412</v>
+        <v>0.439</v>
       </c>
       <c r="J4" t="n">
-        <v>0.364</v>
+        <v>0.401</v>
       </c>
       <c r="K4" t="n">
-        <v>0.309</v>
+        <v>0.344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.25</v>
+        <v>0.297</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2</v>
+        <v>0.244</v>
       </c>
       <c r="N4" t="n">
-        <v>0.154</v>
+        <v>0.197</v>
       </c>
       <c r="O4" t="n">
-        <v>0.103</v>
+        <v>0.156</v>
       </c>
       <c r="P4" t="n">
-        <v>0.082</v>
+        <v>0.109</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.049</v>
+        <v>0.078</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03</v>
+        <v>0.057</v>
       </c>
       <c r="S4" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="V4" t="n">
         <v>0.001</v>
@@ -1285,68 +1189,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.857</v>
+        <v>0.914</v>
       </c>
       <c r="D5" t="n">
-        <v>0.783</v>
+        <v>0.904</v>
       </c>
       <c r="E5" t="n">
-        <v>0.704</v>
+        <v>0.883</v>
       </c>
       <c r="F5" t="n">
-        <v>0.624</v>
+        <v>0.85</v>
       </c>
       <c r="G5" t="n">
-        <v>0.569</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="n">
-        <v>0.506</v>
+        <v>0.778</v>
       </c>
       <c r="I5" t="n">
-        <v>0.452</v>
+        <v>0.734</v>
       </c>
       <c r="J5" t="n">
-        <v>0.389</v>
+        <v>0.674</v>
       </c>
       <c r="K5" t="n">
-        <v>0.336</v>
+        <v>0.605</v>
       </c>
       <c r="L5" t="n">
-        <v>0.285</v>
+        <v>0.547</v>
       </c>
       <c r="M5" t="n">
-        <v>0.246</v>
+        <v>0.483</v>
       </c>
       <c r="N5" t="n">
-        <v>0.191</v>
+        <v>0.413</v>
       </c>
       <c r="O5" t="n">
-        <v>0.153</v>
+        <v>0.335</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.077</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.028</v>
-      </c>
       <c r="T5" t="n">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="U5" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="V5" t="n">
         <v>0.001</v>
@@ -1355,68 +1259,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.863</v>
+        <v>0.875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.788</v>
+        <v>0.83</v>
       </c>
       <c r="E6" t="n">
-        <v>0.712</v>
+        <v>0.789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.622</v>
+        <v>0.756</v>
       </c>
       <c r="G6" t="n">
-        <v>0.552</v>
+        <v>0.708</v>
       </c>
       <c r="H6" t="n">
-        <v>0.502</v>
+        <v>0.681</v>
       </c>
       <c r="I6" t="n">
-        <v>0.439</v>
+        <v>0.634</v>
       </c>
       <c r="J6" t="n">
-        <v>0.401</v>
+        <v>0.595</v>
       </c>
       <c r="K6" t="n">
-        <v>0.344</v>
+        <v>0.555</v>
       </c>
       <c r="L6" t="n">
-        <v>0.297</v>
+        <v>0.504</v>
       </c>
       <c r="M6" t="n">
-        <v>0.244</v>
+        <v>0.46</v>
       </c>
       <c r="N6" t="n">
-        <v>0.197</v>
+        <v>0.388</v>
       </c>
       <c r="O6" t="n">
-        <v>0.156</v>
+        <v>0.325</v>
       </c>
       <c r="P6" t="n">
-        <v>0.109</v>
+        <v>0.281</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.078</v>
+        <v>0.224</v>
       </c>
       <c r="R6" t="n">
-        <v>0.057</v>
+        <v>0.189</v>
       </c>
       <c r="S6" t="n">
-        <v>0.026</v>
+        <v>0.134</v>
       </c>
       <c r="T6" t="n">
-        <v>0.014</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005</v>
+        <v>0.033</v>
       </c>
       <c r="V6" t="n">
         <v>0.001</v>
@@ -1425,68 +1329,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xrai</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.914</v>
+        <v>0.908</v>
       </c>
       <c r="D7" t="n">
-        <v>0.904</v>
+        <v>0.89</v>
       </c>
       <c r="E7" t="n">
-        <v>0.883</v>
+        <v>0.868</v>
       </c>
       <c r="F7" t="n">
-        <v>0.85</v>
+        <v>0.843</v>
       </c>
       <c r="G7" t="n">
         <v>0.82</v>
       </c>
       <c r="H7" t="n">
-        <v>0.778</v>
+        <v>0.792</v>
       </c>
       <c r="I7" t="n">
-        <v>0.734</v>
+        <v>0.741</v>
       </c>
       <c r="J7" t="n">
-        <v>0.674</v>
+        <v>0.704</v>
       </c>
       <c r="K7" t="n">
-        <v>0.605</v>
+        <v>0.67</v>
       </c>
       <c r="L7" t="n">
-        <v>0.547</v>
+        <v>0.639</v>
       </c>
       <c r="M7" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.483</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.335</v>
-      </c>
       <c r="P7" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.185</v>
+        <v>0.337</v>
       </c>
       <c r="R7" t="n">
-        <v>0.126</v>
+        <v>0.253</v>
       </c>
       <c r="S7" t="n">
-        <v>0.077</v>
+        <v>0.178</v>
       </c>
       <c r="T7" t="n">
-        <v>0.029</v>
+        <v>0.105</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01</v>
+        <v>0.041</v>
       </c>
       <c r="V7" t="n">
         <v>0.001</v>
@@ -1495,68 +1399,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.875</v>
+        <v>0.924</v>
       </c>
       <c r="D8" t="n">
-        <v>0.83</v>
+        <v>0.911</v>
       </c>
       <c r="E8" t="n">
-        <v>0.789</v>
+        <v>0.889</v>
       </c>
       <c r="F8" t="n">
-        <v>0.756</v>
+        <v>0.868</v>
       </c>
       <c r="G8" t="n">
-        <v>0.708</v>
+        <v>0.852</v>
       </c>
       <c r="H8" t="n">
-        <v>0.681</v>
+        <v>0.833</v>
       </c>
       <c r="I8" t="n">
-        <v>0.634</v>
+        <v>0.801</v>
       </c>
       <c r="J8" t="n">
-        <v>0.595</v>
+        <v>0.761</v>
       </c>
       <c r="K8" t="n">
-        <v>0.555</v>
+        <v>0.726</v>
       </c>
       <c r="L8" t="n">
-        <v>0.504</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.46</v>
+        <v>0.641</v>
       </c>
       <c r="N8" t="n">
-        <v>0.388</v>
+        <v>0.573</v>
       </c>
       <c r="O8" t="n">
-        <v>0.325</v>
+        <v>0.498</v>
       </c>
       <c r="P8" t="n">
-        <v>0.281</v>
+        <v>0.446</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.224</v>
+        <v>0.357</v>
       </c>
       <c r="R8" t="n">
-        <v>0.189</v>
+        <v>0.272</v>
       </c>
       <c r="S8" t="n">
-        <v>0.134</v>
+        <v>0.195</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="U8" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="V8" t="n">
         <v>0.001</v>
@@ -1565,68 +1469,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.908</v>
+        <v>0.926</v>
       </c>
       <c r="D9" t="n">
-        <v>0.89</v>
+        <v>0.913</v>
       </c>
       <c r="E9" t="n">
-        <v>0.868</v>
+        <v>0.895</v>
       </c>
       <c r="F9" t="n">
-        <v>0.843</v>
+        <v>0.879</v>
       </c>
       <c r="G9" t="n">
-        <v>0.82</v>
+        <v>0.872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.792</v>
+        <v>0.848</v>
       </c>
       <c r="I9" t="n">
-        <v>0.741</v>
+        <v>0.822</v>
       </c>
       <c r="J9" t="n">
-        <v>0.704</v>
+        <v>0.791</v>
       </c>
       <c r="K9" t="n">
-        <v>0.67</v>
+        <v>0.761</v>
       </c>
       <c r="L9" t="n">
-        <v>0.639</v>
+        <v>0.721</v>
       </c>
       <c r="M9" t="n">
-        <v>0.597</v>
+        <v>0.669</v>
       </c>
       <c r="N9" t="n">
-        <v>0.539</v>
+        <v>0.594</v>
       </c>
       <c r="O9" t="n">
-        <v>0.483</v>
+        <v>0.522</v>
       </c>
       <c r="P9" t="n">
-        <v>0.42</v>
+        <v>0.458</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.337</v>
+        <v>0.37</v>
       </c>
       <c r="R9" t="n">
-        <v>0.253</v>
+        <v>0.276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.178</v>
+        <v>0.162</v>
       </c>
       <c r="T9" t="n">
-        <v>0.105</v>
+        <v>0.067</v>
       </c>
       <c r="U9" t="n">
-        <v>0.041</v>
+        <v>0.019</v>
       </c>
       <c r="V9" t="n">
         <v>0.001</v>
@@ -1635,68 +1539,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.924</v>
+        <v>0.926</v>
       </c>
       <c r="D10" t="n">
-        <v>0.911</v>
+        <v>0.909</v>
       </c>
       <c r="E10" t="n">
-        <v>0.889</v>
+        <v>0.894</v>
       </c>
       <c r="F10" t="n">
-        <v>0.868</v>
+        <v>0.888</v>
       </c>
       <c r="G10" t="n">
-        <v>0.852</v>
+        <v>0.874</v>
       </c>
       <c r="H10" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.833</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.801</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.761</v>
+        <v>0.805</v>
       </c>
       <c r="K10" t="n">
-        <v>0.726</v>
+        <v>0.776</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.737</v>
       </c>
       <c r="M10" t="n">
-        <v>0.641</v>
+        <v>0.676</v>
       </c>
       <c r="N10" t="n">
-        <v>0.573</v>
+        <v>0.627</v>
       </c>
       <c r="O10" t="n">
-        <v>0.498</v>
+        <v>0.546</v>
       </c>
       <c r="P10" t="n">
-        <v>0.446</v>
+        <v>0.473</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.357</v>
+        <v>0.396</v>
       </c>
       <c r="R10" t="n">
-        <v>0.272</v>
+        <v>0.296</v>
       </c>
       <c r="S10" t="n">
-        <v>0.195</v>
+        <v>0.192</v>
       </c>
       <c r="T10" t="n">
-        <v>0.097</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="V10" t="n">
         <v>0.001</v>
@@ -1705,285 +1609,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.926</v>
+        <v>0.921</v>
       </c>
       <c r="D11" t="n">
-        <v>0.913</v>
+        <v>0.903</v>
       </c>
       <c r="E11" t="n">
-        <v>0.895</v>
+        <v>0.894</v>
       </c>
       <c r="F11" t="n">
-        <v>0.879</v>
+        <v>0.881</v>
       </c>
       <c r="G11" t="n">
-        <v>0.872</v>
+        <v>0.869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.848</v>
+        <v>0.847</v>
       </c>
       <c r="I11" t="n">
-        <v>0.822</v>
+        <v>0.838</v>
       </c>
       <c r="J11" t="n">
-        <v>0.791</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.761</v>
+        <v>0.779</v>
       </c>
       <c r="L11" t="n">
-        <v>0.721</v>
+        <v>0.755</v>
       </c>
       <c r="M11" t="n">
-        <v>0.669</v>
+        <v>0.713</v>
       </c>
       <c r="N11" t="n">
-        <v>0.594</v>
+        <v>0.651</v>
       </c>
       <c r="O11" t="n">
-        <v>0.522</v>
+        <v>0.604</v>
       </c>
       <c r="P11" t="n">
-        <v>0.458</v>
+        <v>0.532</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.37</v>
+        <v>0.433</v>
       </c>
       <c r="R11" t="n">
-        <v>0.276</v>
+        <v>0.317</v>
       </c>
       <c r="S11" t="n">
-        <v>0.162</v>
+        <v>0.223</v>
       </c>
       <c r="T11" t="n">
-        <v>0.067</v>
+        <v>0.107</v>
       </c>
       <c r="U11" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="V11" t="n">
         <v>0.001</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dinov2_COMBO_FIXED</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.894</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.853</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>occlusion</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.894</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.881</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>grad_cam</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V14">
+  <conditionalFormatting sqref="B2:V11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
